--- a/artfynd/A 28930-2025 artfynd.xlsx
+++ b/artfynd/A 28930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126627791</v>
       </c>
       <c r="B2" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>126630080</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>126631030</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126630544</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126628290</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>126628759</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126628369</v>
       </c>
       <c r="B9" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126629497</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>126627956</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28930-2025 artfynd.xlsx
+++ b/artfynd/A 28930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126627791</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>126630080</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>126631030</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126630544</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126628290</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>126628759</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126628369</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126629497</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>126627956</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28930-2025 artfynd.xlsx
+++ b/artfynd/A 28930-2025 artfynd.xlsx
@@ -1192,60 +1192,64 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126630796</v>
+        <v>126628290</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andrakebyn 112, Dlr</t>
+          <t>Andrakebyn 112, Andrakebyn 112, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538178</v>
+        <v>538141</v>
       </c>
       <c r="R6" t="n">
-        <v>6709285</v>
+        <v>6709323</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,8 +1297,14 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1311,64 +1321,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126628290</v>
+        <v>126630796</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>58027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andrakebyn 112, Andrakebyn 112, Dlr</t>
+          <t>Andrakebyn 112, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538141</v>
+        <v>538178</v>
       </c>
       <c r="R7" t="n">
-        <v>6709323</v>
+        <v>6709285</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1397,7 +1403,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1407,7 +1413,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,14 +1422,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">

--- a/artfynd/A 28930-2025 artfynd.xlsx
+++ b/artfynd/A 28930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126627791</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>126630080</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>126631030</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126630544</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1192,64 +1192,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126628290</v>
+        <v>126630796</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>58027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andrakebyn 112, Andrakebyn 112, Dlr</t>
+          <t>Andrakebyn 112, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538141</v>
+        <v>538178</v>
       </c>
       <c r="R6" t="n">
-        <v>6709323</v>
+        <v>6709285</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1278,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,14 +1293,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1321,60 +1311,64 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126630796</v>
+        <v>126628290</v>
       </c>
       <c r="B7" t="n">
-        <v>58027</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andrakebyn 112, Dlr</t>
+          <t>Andrakebyn 112, Andrakebyn 112, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538178</v>
+        <v>538141</v>
       </c>
       <c r="R7" t="n">
-        <v>6709285</v>
+        <v>6709323</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1403,7 +1397,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1413,7 +1407,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,8 +1416,14 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1443,7 +1443,7 @@
         <v>126628759</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126628369</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126629497</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>126627956</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28930-2025 artfynd.xlsx
+++ b/artfynd/A 28930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126627791</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>126630080</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>126631030</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126630544</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126628290</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>126628759</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126628369</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126629497</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>126627956</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28930-2025 artfynd.xlsx
+++ b/artfynd/A 28930-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126627791</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>126630080</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>126631030</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126630544</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>126628290</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>126628759</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126628369</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>126629497</v>
       </c>
       <c r="B10" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>126627956</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
